--- a/timestamps_temp/imaging_timestamp.xlsx
+++ b/timestamps_temp/imaging_timestamp.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Microfluidics\Roche_2025\Ahadiyan_2025\20250627 - Qconst 10% nutrient (successful) [BRC]\logs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamidrezaahadiya\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4635305-6CA5-4D25-AAAF-243ECED269D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{395B7E91-639D-4F94-B38A-E2D046B8EF5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17340" yWindow="2030" windowWidth="28710" windowHeight="17030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16605" yWindow="3645" windowWidth="9180" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,15 +37,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>Image#</t>
   </si>
   <si>
-    <t>Absolute Time</t>
-  </si>
-  <si>
-    <t>Date</t>
+    <t>Datetime</t>
   </si>
 </sst>
 </file>
@@ -55,9 +52,9 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="yyyy/m/d\ h:mm:ss"/>
-    <numFmt numFmtId="167" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="169" formatCode="m/d/yyyy\ h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -67,14 +64,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -102,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -110,12 +99,8 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -396,25 +381,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T45"/>
+  <dimension ref="A1:R91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>2</v>
-      </c>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
@@ -425,23 +407,20 @@
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
       <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>0</v>
       </c>
-      <c r="B2" s="8">
-        <v>0.76732638888888893</v>
-      </c>
-      <c r="C2" s="11">
-        <v>46025</v>
-      </c>
+      <c r="B2" s="7">
+        <v>46083.820115740738</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
@@ -453,522 +432,818 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="7">
         <f>B2+TIME(0,30,0)</f>
-        <v>0.7881597222222223</v>
-      </c>
-      <c r="C3" s="11">
-        <v>46025</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+        <v>46083.840949074074</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="8">
-        <v>0.80899305555555601</v>
-      </c>
-      <c r="C4" s="11">
-        <v>46025</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B4" s="7">
+        <f>B3+TIME(0,30,0)</f>
+        <v>46083.86178240741</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="8">
-        <f t="shared" ref="B5:B45" si="0">B4+TIME(0,30,0)</f>
-        <v>0.82982638888888938</v>
-      </c>
-      <c r="C5" s="11">
-        <v>46025</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B5" s="7">
+        <f t="shared" ref="B5:B54" si="0">B4+TIME(0,30,0)</f>
+        <v>46083.882615740746</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="8">
-        <v>0.85065972222222197</v>
-      </c>
-      <c r="C6" s="11">
-        <v>46025</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B6" s="7">
+        <f t="shared" si="0"/>
+        <v>46083.903449074081</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="8">
-        <f t="shared" ref="B7:B45" si="1">B6+TIME(0,30,0)</f>
-        <v>0.87149305555555534</v>
-      </c>
-      <c r="C7" s="11">
-        <v>46025</v>
-      </c>
+      <c r="B7" s="7">
+        <f t="shared" si="0"/>
+        <v>46083.924282407417</v>
+      </c>
+      <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B8" s="8">
-        <v>0.89232638888888904</v>
-      </c>
-      <c r="C8" s="11">
-        <v>46025</v>
-      </c>
+      <c r="B8" s="7">
+        <f t="shared" si="0"/>
+        <v>46083.945115740753</v>
+      </c>
+      <c r="C8" s="5"/>
       <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
       <c r="F8" s="5"/>
-      <c r="H8" s="5"/>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B9" s="8">
-        <f t="shared" ref="B9:B45" si="2">B8+TIME(0,30,0)</f>
-        <v>0.91315972222222241</v>
-      </c>
-      <c r="C9" s="11">
-        <v>46025</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B9" s="7">
+        <v>46083.973310185182</v>
+      </c>
+      <c r="C9" s="5"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>8</v>
       </c>
-      <c r="B10" s="8">
-        <v>0.93399305555555601</v>
-      </c>
-      <c r="C10" s="11">
-        <v>46025</v>
-      </c>
+      <c r="B10" s="7">
+        <f t="shared" si="0"/>
+        <v>46083.994143518517</v>
+      </c>
+      <c r="C10" s="5"/>
       <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
       <c r="F10" s="5"/>
-      <c r="H10" s="5"/>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>9</v>
       </c>
-      <c r="B11" s="8">
-        <f t="shared" ref="B11:B45" si="3">B10+TIME(0,30,0)</f>
-        <v>0.95482638888888938</v>
-      </c>
-      <c r="C11" s="11">
-        <v>46025</v>
-      </c>
+      <c r="B11" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.014976851853</v>
+      </c>
+      <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>10</v>
       </c>
-      <c r="B12" s="8">
-        <v>0.97565972222222197</v>
-      </c>
-      <c r="C12" s="11">
-        <v>46025</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B12" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.035810185189</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>11</v>
       </c>
-      <c r="B13" s="8">
-        <f t="shared" ref="B13:B45" si="4">B12+TIME(0,30,0)</f>
-        <v>0.99649305555555534</v>
-      </c>
-      <c r="C13" s="11">
-        <v>46025</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B13" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.056643518525</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B14" s="8">
-        <v>1.0173263888888899</v>
-      </c>
-      <c r="C14" s="12">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B14" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.07747685186</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B15" s="8">
-        <f t="shared" ref="B15:B45" si="5">B14+TIME(0,30,0)</f>
-        <v>1.0381597222222232</v>
-      </c>
-      <c r="C15" s="12">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B15" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.098310185196</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>14</v>
       </c>
-      <c r="B16" s="8">
-        <v>1.05899305555556</v>
-      </c>
-      <c r="C16" s="12">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.119143518532</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>15</v>
       </c>
-      <c r="B17" s="8">
-        <f t="shared" ref="B17:B45" si="6">B16+TIME(0,30,0)</f>
-        <v>1.0798263888888933</v>
-      </c>
-      <c r="C17" s="12">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.139976851868</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B18" s="8">
-        <v>1.1006597222222201</v>
-      </c>
-      <c r="C18" s="12">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.160810185203</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>17</v>
       </c>
-      <c r="B19" s="8">
-        <f t="shared" ref="B19:B45" si="7">B18+TIME(0,30,0)</f>
-        <v>1.1214930555555533</v>
-      </c>
-      <c r="C19" s="12">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.181643518539</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>18</v>
       </c>
-      <c r="B20" s="8">
-        <v>1.1423263888888899</v>
-      </c>
-      <c r="C20" s="12">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.202476851875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>19</v>
       </c>
-      <c r="B21" s="8">
-        <f t="shared" ref="B21:B45" si="8">B20+TIME(0,30,0)</f>
-        <v>1.1631597222222232</v>
-      </c>
-      <c r="C21" s="12">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.223310185211</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>20</v>
       </c>
-      <c r="B22" s="8">
-        <v>1.18399305555556</v>
-      </c>
-      <c r="C22" s="12">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.244143518546</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>21</v>
       </c>
-      <c r="B23" s="8">
-        <f t="shared" ref="B23:B45" si="9">B22+TIME(0,30,0)</f>
-        <v>1.2048263888888933</v>
-      </c>
-      <c r="C23" s="12">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.264976851882</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>22</v>
       </c>
-      <c r="B24" s="8">
-        <v>1.2256597222222201</v>
-      </c>
-      <c r="C24" s="12">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.285810185218</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>23</v>
       </c>
-      <c r="B25" s="8">
-        <f t="shared" ref="B25:B45" si="10">B24+TIME(0,30,0)</f>
-        <v>1.2464930555555533</v>
-      </c>
-      <c r="C25" s="12">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.306643518554</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>24</v>
       </c>
-      <c r="B26" s="8">
-        <v>1.2673263888888899</v>
-      </c>
-      <c r="C26" s="12">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.32747685189</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>25</v>
       </c>
-      <c r="B27" s="8">
-        <f t="shared" ref="B27:B45" si="11">B26+TIME(0,30,0)</f>
-        <v>1.2881597222222232</v>
-      </c>
-      <c r="C27" s="12">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.348310185225</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>26</v>
       </c>
-      <c r="B28" s="8">
-        <v>1.30899305555556</v>
-      </c>
-      <c r="C28" s="12">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.369143518561</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>27</v>
       </c>
-      <c r="B29" s="8">
-        <f t="shared" ref="B29:B45" si="12">B28+TIME(0,30,0)</f>
-        <v>1.3298263888888933</v>
-      </c>
-      <c r="C29" s="12">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.389976851897</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>28</v>
       </c>
-      <c r="B30" s="8">
-        <v>1.3506597222222201</v>
-      </c>
-      <c r="C30" s="12">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.410810185233</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>29</v>
       </c>
-      <c r="B31" s="8">
-        <f t="shared" ref="B31:B45" si="13">B30+TIME(0,30,0)</f>
-        <v>1.3714930555555533</v>
-      </c>
-      <c r="C31" s="12">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.431643518568</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>30</v>
       </c>
-      <c r="B32" s="8">
-        <v>1.3923263888888899</v>
-      </c>
-      <c r="C32" s="12">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.452476851904</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>31</v>
       </c>
-      <c r="B33" s="8">
-        <f t="shared" ref="B33:B45" si="14">B32+TIME(0,30,0)</f>
-        <v>1.4131597222222232</v>
-      </c>
-      <c r="C33" s="12">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.47331018524</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>32</v>
       </c>
-      <c r="B34" s="8">
-        <v>1.43399305555556</v>
-      </c>
-      <c r="C34" s="12">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.494143518576</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>33</v>
       </c>
-      <c r="B35" s="8">
-        <f t="shared" ref="B35:B45" si="15">B34+TIME(0,30,0)</f>
-        <v>1.4548263888888933</v>
-      </c>
-      <c r="C35" s="12">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.514976851911</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>34</v>
       </c>
-      <c r="B36" s="8">
-        <v>1.4756597222222201</v>
-      </c>
-      <c r="C36" s="12">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.535810185247</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>35</v>
       </c>
-      <c r="B37" s="8">
-        <f t="shared" ref="B37:B45" si="16">B36+TIME(0,30,0)</f>
-        <v>1.4964930555555533</v>
-      </c>
-      <c r="C37" s="12">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.556643518583</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>36</v>
       </c>
-      <c r="B38" s="8">
-        <v>1.5173263888888899</v>
-      </c>
-      <c r="C38" s="12">
-        <v>46027</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.577476851919</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>37</v>
       </c>
-      <c r="B39" s="8">
-        <f t="shared" ref="B39:B45" si="17">B38+TIME(0,30,0)</f>
-        <v>1.5381597222222232</v>
-      </c>
-      <c r="C39" s="12">
-        <v>46027</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.598310185254</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>38</v>
       </c>
-      <c r="B40" s="8">
-        <v>1.55899305555556</v>
-      </c>
-      <c r="C40" s="12">
-        <v>46027</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.61914351859</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>39</v>
       </c>
-      <c r="B41" s="8">
-        <f t="shared" ref="B41:B45" si="18">B40+TIME(0,30,0)</f>
-        <v>1.5798263888888933</v>
-      </c>
-      <c r="C41" s="12">
-        <v>46027</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.639976851926</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>40</v>
       </c>
-      <c r="B42" s="8">
-        <v>1.6006597222222201</v>
-      </c>
-      <c r="C42" s="12">
-        <v>46027</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.660810185262</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>41</v>
       </c>
-      <c r="B43" s="8">
-        <f t="shared" ref="B43:B45" si="19">B42+TIME(0,30,0)</f>
-        <v>1.6214930555555533</v>
-      </c>
-      <c r="C43" s="12">
-        <v>46027</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.681643518597</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>42</v>
       </c>
-      <c r="B44" s="8">
-        <v>1.6423263888888899</v>
-      </c>
-      <c r="C44" s="12">
-        <v>46027</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.702476851933</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43</v>
       </c>
-      <c r="B45" s="8">
-        <f t="shared" ref="B45" si="20">B44+TIME(0,30,0)</f>
-        <v>1.6631597222222232</v>
-      </c>
-      <c r="C45" s="12">
-        <v>46027</v>
+      <c r="B45" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.723310185269</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <v>44</v>
+      </c>
+      <c r="B46" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.744143518605</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <v>45</v>
+      </c>
+      <c r="B47" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.76497685194</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <v>46</v>
+      </c>
+      <c r="B48" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.785810185276</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <v>47</v>
+      </c>
+      <c r="B49" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.806643518612</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <v>48</v>
+      </c>
+      <c r="B50" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.827476851948</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <v>49</v>
+      </c>
+      <c r="B51" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.848310185283</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <v>50</v>
+      </c>
+      <c r="B52" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.869143518619</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
+        <v>51</v>
+      </c>
+      <c r="B53" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.889976851955</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <v>52</v>
+      </c>
+      <c r="B54" s="7">
+        <f t="shared" si="0"/>
+        <v>46084.910810185291</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
+        <v>53</v>
+      </c>
+      <c r="B55" s="7">
+        <v>46084.92659722222</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="6">
+        <v>54</v>
+      </c>
+      <c r="B56" s="7">
+        <f>B55+TIME(1,0,0)</f>
+        <v>46084.968263888884</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="6">
+        <v>55</v>
+      </c>
+      <c r="B57" s="7">
+        <f t="shared" ref="B57:B90" si="1">B56+TIME(1,0,0)</f>
+        <v>46085.009930555549</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="6">
+        <v>56</v>
+      </c>
+      <c r="B58" s="7">
+        <f t="shared" si="1"/>
+        <v>46085.051597222213</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="6">
+        <v>57</v>
+      </c>
+      <c r="B59" s="7">
+        <f t="shared" si="1"/>
+        <v>46085.093263888877</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="6">
+        <v>58</v>
+      </c>
+      <c r="B60" s="7">
+        <f t="shared" si="1"/>
+        <v>46085.134930555541</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="6">
+        <v>59</v>
+      </c>
+      <c r="B61" s="7">
+        <f t="shared" si="1"/>
+        <v>46085.176597222206</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="6">
+        <v>60</v>
+      </c>
+      <c r="B62" s="7">
+        <f t="shared" si="1"/>
+        <v>46085.21826388887</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="6">
+        <v>61</v>
+      </c>
+      <c r="B63" s="7">
+        <f t="shared" si="1"/>
+        <v>46085.259930555534</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="6">
+        <v>62</v>
+      </c>
+      <c r="B64" s="7">
+        <f t="shared" si="1"/>
+        <v>46085.301597222198</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="6">
+        <v>63</v>
+      </c>
+      <c r="B65" s="7">
+        <f t="shared" si="1"/>
+        <v>46085.343263888863</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="6">
+        <v>64</v>
+      </c>
+      <c r="B66" s="7">
+        <f t="shared" si="1"/>
+        <v>46085.384930555527</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
+        <v>65</v>
+      </c>
+      <c r="B67" s="7">
+        <f t="shared" si="1"/>
+        <v>46085.426597222191</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="6">
+        <v>66</v>
+      </c>
+      <c r="B68" s="7">
+        <f t="shared" si="1"/>
+        <v>46085.468263888855</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="6">
+        <v>67</v>
+      </c>
+      <c r="B69" s="7">
+        <f t="shared" si="1"/>
+        <v>46085.50993055552</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="6">
+        <v>68</v>
+      </c>
+      <c r="B70" s="7">
+        <f t="shared" si="1"/>
+        <v>46085.551597222184</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="6">
+        <v>69</v>
+      </c>
+      <c r="B71" s="7">
+        <f t="shared" si="1"/>
+        <v>46085.593263888848</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
+        <v>70</v>
+      </c>
+      <c r="B72" s="7">
+        <f t="shared" si="1"/>
+        <v>46085.634930555512</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="6">
+        <v>71</v>
+      </c>
+      <c r="B73" s="7">
+        <f t="shared" si="1"/>
+        <v>46085.676597222176</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="6">
+        <v>72</v>
+      </c>
+      <c r="B74" s="7">
+        <f t="shared" si="1"/>
+        <v>46085.718263888841</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="6">
+        <v>73</v>
+      </c>
+      <c r="B75" s="7">
+        <f t="shared" si="1"/>
+        <v>46085.759930555505</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="6">
+        <v>74</v>
+      </c>
+      <c r="B76" s="7">
+        <f t="shared" si="1"/>
+        <v>46085.801597222169</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="6">
+        <v>75</v>
+      </c>
+      <c r="B77" s="7">
+        <f t="shared" si="1"/>
+        <v>46085.843263888833</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="6">
+        <v>76</v>
+      </c>
+      <c r="B78" s="7">
+        <f t="shared" si="1"/>
+        <v>46085.884930555498</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="6">
+        <v>77</v>
+      </c>
+      <c r="B79" s="7">
+        <f t="shared" si="1"/>
+        <v>46085.926597222162</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="6">
+        <v>78</v>
+      </c>
+      <c r="B80" s="7">
+        <f>B79+TIME(1,0,0)</f>
+        <v>46085.968263888826</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="6">
+        <v>79</v>
+      </c>
+      <c r="B81" s="7">
+        <f t="shared" si="1"/>
+        <v>46086.00993055549</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="6">
+        <v>80</v>
+      </c>
+      <c r="B82" s="7">
+        <f t="shared" si="1"/>
+        <v>46086.051597222155</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="6">
+        <v>81</v>
+      </c>
+      <c r="B83" s="7">
+        <f t="shared" si="1"/>
+        <v>46086.093263888819</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="6">
+        <v>82</v>
+      </c>
+      <c r="B84" s="7">
+        <f t="shared" si="1"/>
+        <v>46086.134930555483</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="6">
+        <v>83</v>
+      </c>
+      <c r="B85" s="7">
+        <f t="shared" si="1"/>
+        <v>46086.176597222147</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="6">
+        <v>84</v>
+      </c>
+      <c r="B86" s="7">
+        <f t="shared" si="1"/>
+        <v>46086.218263888812</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="6">
+        <v>85</v>
+      </c>
+      <c r="B87" s="7">
+        <f t="shared" si="1"/>
+        <v>46086.259930555476</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
+        <v>86</v>
+      </c>
+      <c r="B88" s="7">
+        <f t="shared" si="1"/>
+        <v>46086.30159722214</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
+        <v>87</v>
+      </c>
+      <c r="B89" s="7">
+        <f t="shared" si="1"/>
+        <v>46086.343263888804</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="6">
+        <v>88</v>
+      </c>
+      <c r="B90" s="7">
+        <f t="shared" si="1"/>
+        <v>46086.384930555469</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="6">
+        <v>89</v>
+      </c>
+      <c r="B91" s="7">
+        <v>46087.5781712963</v>
       </c>
     </row>
   </sheetData>
